--- a/reports/Extent-Report/Zlaata-QAResults.xlsx
+++ b/reports/Extent-Report/Zlaata-QAResults.xlsx
@@ -189,34 +189,34 @@
     <t>device</t>
   </si>
   <si>
-    <t>Jun 20, 2025 10:04:09 am</t>
+    <t>Aug 20, 2025 9:36:13 am</t>
   </si>
   <si>
-    <t>Jun 20, 2025 10:02:45 am</t>
+    <t>Aug 20, 2025 9:35:07 am</t>
   </si>
   <si>
-    <t>Jun 20, 2025 10:04:07 am</t>
+    <t>Aug 20, 2025 9:36:11 am</t>
   </si>
   <si>
-    <t>1 m 22.809 s</t>
+    <t>1 m 4.249 s</t>
   </si>
   <si>
     <t>100%</t>
   </si>
   <si>
-    <t>TC_UI_Zlaata_ADDP_04 | Verify Add New Address functionality on checkoutpage | "TD_UI_Zlaata_ADDP_04"</t>
+    <t>TC_UI_Zlaata_CP_16 | Verify Apply and Remove button in coupon text box and in coupon pop up | "TD_UI_Zlaata_CP_16"</t>
   </si>
   <si>
-    <t>1 m 22.239 s</t>
+    <t>1 m 3.667 s</t>
   </si>
   <si>
-    <t>address Page Feature</t>
+    <t>Coupon Section</t>
   </si>
   <si>
-    <t>@TC_UI_Zlaata_ADDP_04</t>
+    <t>@TC_UI_Zlaata_CP_16</t>
   </si>
   <si>
-    <t>1 m 22.244 s</t>
+    <t>1 m 3.674 s</t>
   </si>
 </sst>
 </file>
@@ -1788,7 +1788,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ADDP_04 | Verify Add New Address functionality on checkoutpage | "TD_UI_Zlaata_ADDP_04"</c:v>
+                  <c:v>TC_UI_Zlaata_CP_16 | Verify Apply and Remove button in coupon text box and in coupon pop up | "TD_UI_Zlaata_CP_16"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1799,7 +1799,7 @@
               <c:numCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>1.0</c:v>
+                  <c:v>6.0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1860,7 +1860,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ADDP_04 | Verify Add New Address functionality on checkoutpage | "TD_UI_Zlaata_ADDP_04"</c:v>
+                  <c:v>TC_UI_Zlaata_CP_16 | Verify Apply and Remove button in coupon text box and in coupon pop up | "TD_UI_Zlaata_CP_16"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1927,7 +1927,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>TC_UI_Zlaata_ADDP_04 | Verify Add New Address functionality on checkoutpage | "TD_UI_Zlaata_ADDP_04"</c:v>
+                  <c:v>TC_UI_Zlaata_CP_16 | Verify Apply and Remove button in coupon text box and in coupon pop up | "TD_UI_Zlaata_CP_16"</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2334,7 +2334,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ADDP_04</c:v>
+                  <c:v>@TC_UI_Zlaata_CP_16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2407,7 +2407,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ADDP_04</c:v>
+                  <c:v>@TC_UI_Zlaata_CP_16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2475,7 +2475,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>@TC_UI_Zlaata_ADDP_04</c:v>
+                  <c:v>@TC_UI_Zlaata_CP_16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2691,7 +2691,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>address Page Feature</c:v>
+                  <c:v>Coupon Section</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2763,7 +2763,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>address Page Feature</c:v>
+                  <c:v>Coupon Section</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2830,7 +2830,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>address Page Feature</c:v>
+                  <c:v>Coupon Section</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5770,7 +5770,7 @@
     <col min="7" max="7" customWidth="true" width="20.85546875"/>
   </cols>
   <sheetData/>
-  <sheetProtection sheet="true" password="E929" scenarios="true" objects="true"/>
+  <sheetProtection sheet="true" password="CCB5" scenarios="true" objects="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5854,10 +5854,10 @@
         <v>29</v>
       </c>
       <c r="G22" s="57" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="H22" s="58" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="I22" s="59"/>
       <c r="J22" s="60"/>
@@ -6078,10 +6078,10 @@
         <v>54</v>
       </c>
       <c r="J22" s="57" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="K22" s="58" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="L22" s="59"/>
       <c r="M22" s="60"/>
@@ -6155,7 +6155,7 @@
         <v>12</v>
       </c>
       <c r="H2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H5" t="n" s="0">
         <f>SUM(H2:H4)</f>
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
